--- a/画像差し替え/eBay画像差し替え_2026-09-30_反映結果.xlsx
+++ b/画像差し替え/eBay画像差し替え_2026-09-30_反映結果.xlsx
@@ -70,7 +70,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +102,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,6 +181,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -820,9 +828,9 @@
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n"/>
       <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z3" s="17" t="inlineStr">
+        <is>
+          <t>見送り：メルカリ品は約23cmのぬいぐるみ。eBayはボールチェーン付きマスコットで別商品</t>
         </is>
       </c>
     </row>
@@ -1356,9 +1364,9 @@
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n"/>
       <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z10" s="17" t="inlineStr">
+        <is>
+          <t>見送り：メルカリShopsの画像サーバーがこの環境のネットワーク方針でブロックされ取得不可</t>
         </is>
       </c>
     </row>
@@ -1416,9 +1424,9 @@
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z11" s="17" t="inlineStr">
+        <is>
+          <t>見送り：メルカリ3枚のうち2枚はeBay現行と同じ、残り1枚は303pxでeBay基準（500px）未満</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1454,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>候補なし</t>
+          <t>メルカリ売り切れ ＋ eBay現行画像</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1454,31 +1462,81 @@
           <t>https://jp.mercari.com/item/m62694654811</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>未開封4パックの出品なし（候補はバラのカードのまとめ売り）</t>
+          <t>未開封4パック（赤・緑・青・黄）。eBay現行2枚（ケース入り）＋メルカリの表裏10枚＝12枚</t>
         </is>
       </c>
       <c r="J12" s="3" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z12" s="11" t="inlineStr">
+        <is>
+          <t>更新済 2→12枚</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1860,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>候補なし</t>
+          <t>メルカリ売り切れ ＋ eBay現行画像</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1810,17 +1868,35 @@
           <t>https://jp.mercari.com/item/m98373505806</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>ヤフオク/PayPayフリマで一致する出品なし（メルカリ未検索）</t>
+          <t>袋入り未開封のピンバッジ。eBay現行1枚＋メルカリの表・側面・裏3枚＝4枚</t>
         </is>
       </c>
       <c r="J17" s="3" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
@@ -1832,9 +1908,9 @@
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n"/>
       <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z17" s="11" t="inlineStr">
+        <is>
+          <t>更新済 1→4枚</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2216,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>候補なし</t>
+          <t>メルカリ売り切れ ＋ eBay現行画像</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -2148,17 +2224,35 @@
           <t>https://jp.mercari.com/item/m14155454041</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>ヤフオク/PayPayフリマで一致する出品なし（メルカリ未検索）</t>
+          <t>ゴールデントランプ未開封箱。eBay現行2枚＋メルカリ表裏2枚＝4枚（3枚目はスマホ画面のスクショのため除外）</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
       <c r="O21" s="4" t="n"/>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
@@ -2170,9 +2264,9 @@
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z21" s="11" t="inlineStr">
+        <is>
+          <t>更新済 2→4枚</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2294,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>候補なし</t>
+          <t>メルカリ売り切れ</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2208,31 +2302,89 @@
           <t>https://jp.mercari.com/item/m58816222389</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>ヤフオク/PayPayフリマで一致する出品なし（メルカリ未検索）</t>
+          <t>Pullip リーマ DAYAN 40th 未開封箱。eBay現行2枚はメルカリ1・2枚目と同じ。12枚目は362pxでeBay基準（500px）未満のため除外し14枚</t>
         </is>
       </c>
       <c r="J22" s="3" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
-      <c r="T22" s="4" t="n"/>
-      <c r="U22" s="4" t="n"/>
-      <c r="V22" s="4" t="n"/>
-      <c r="W22" s="4" t="n"/>
-      <c r="X22" s="4" t="n"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
       <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z22" s="11" t="inlineStr">
+        <is>
+          <t>更新済 2→14枚</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2468,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>候補なし</t>
+          <t>メルカリ売り切れ ＋ eBay現行画像</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -2324,17 +2476,35 @@
           <t>https://jp.mercari.com/item/m68544308624</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n"/>
+      <c r="H24" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>ヤフオク/PayPayフリマで一致する出品なし（メルカリ未検索）</t>
+          <t>マチカネフクキタル＆ニャーさん 袋入り未開封。eBay現行1枚＋メルカリ3枚＝4枚</t>
         </is>
       </c>
       <c r="J24" s="3" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
@@ -2346,9 +2516,9 @@
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="10" t="inlineStr">
-        <is>
-          <t>保留：メルカリ画像未取得（画像1〜が空）</t>
+      <c r="Z24" s="11" t="inlineStr">
+        <is>
+          <t>更新済 1→4枚</t>
         </is>
       </c>
     </row>
@@ -2897,83 +3067,121 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V22" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
@@ -7572,7 +7780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7901,13 +8109,121 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>昇格8件の反映結果（追記）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>430</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>更新済 2→12枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>571</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>更新済 1→4枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>624</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>更新済 2→4枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>645</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>更新済 2→14枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>686</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>更新済 1→4枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>321</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>見送り：メルカリ品は約23cmのぬいぐるみ。eBayはボールチェーン付きマスコットで別商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>375</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>見送り：メルカリShopsの画像サーバーがこの環境のネットワーク方針でブロックされ取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>381</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>見送り：メルカリ3枚のうち2枚はeBay現行と同じ、残り1枚は303pxでeBay基準（500px）未満</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>321は昇格時の見落としとは別に、商品の種類違い（ぬいぐるみ／マスコット）に注意。サイズ・ボールチェーンの有無も照合項目に加える</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="18">
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B16:D16"/>
